--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4652,43 +4652,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122569536</v>
+        <v>137452549</v>
       </c>
       <c r="B34" t="n">
-        <v>80657</v>
+        <v>58876</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228430</v>
+        <v>208245</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Norredatorp, Norredatorp, Upl</t>
+          <t>Eda, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>662958</v>
+        <v>662979</v>
       </c>
       <c r="R34" t="n">
-        <v>6634243</v>
+        <v>6634214</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4712,22 +4717,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4742,16 +4747,123 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Karla Alfaro Gripe</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137452549</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122569536</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80657</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norredatorp, Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>662958</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6634243</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122569536</t>
         </is>
@@ -4792,6 +4904,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7444-2023 artfynd.xlsx
+++ b/artfynd/A 7444-2023 artfynd.xlsx
@@ -4655,7 +4655,7 @@
         <v>137452549</v>
       </c>
       <c r="B34" t="n">
-        <v>58876</v>
+        <v>58879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
